--- a/system_development/Moultrie/v0.3/cart/BOM-v0.3-cart.xlsx
+++ b/system_development/Moultrie/v0.3/cart/BOM-v0.3-cart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\flow-through-water-quality-system\system_development\Moultrie\v0.3\cart\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mk103\Documents\GitHub\flowthrough-water-quality-monitoring-system\system_development\Moultrie\v0.3\cart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9137B9B-C6E1-41BB-A76E-3D7387188CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A93A822-D71C-411F-B407-FE7936545BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t>Total Cost</t>
   </si>
@@ -171,6 +171,15 @@
   </si>
   <si>
     <t>Multipurpose 6061 Aluminum Sheet, 1/8" Thick, 12" x 12"</t>
+  </si>
+  <si>
+    <t>HDPE Sheet: 0.25 in Thick, 24 in x 24 in, Opaque, Off-White, 4,600 psi Tensile Strength</t>
+  </si>
+  <si>
+    <t>HPDE Sheet</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/HDPE-Sheet-0-25-in-Thick-1ZAL8</t>
   </si>
 </sst>
 </file>
@@ -688,7 +697,7 @@
         <v>19.989999999999998</v>
       </c>
       <c r="E4" s="6">
-        <f t="shared" ref="E4:E12" si="0">C4*D4</f>
+        <f t="shared" ref="E4:E13" si="0">C4*D4</f>
         <v>19.989999999999998</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -878,12 +887,25 @@
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="3"/>
+      <c r="A13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+      <c r="D13" s="6">
+        <v>31.19</v>
+      </c>
+      <c r="E13" s="6">
+        <f t="shared" si="0"/>
+        <v>62.38</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
@@ -958,7 +980,7 @@
       </c>
       <c r="E21" s="8">
         <f>SUM(E2:E20)</f>
-        <v>510.45</v>
+        <v>572.83000000000004</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1125,7 +1147,7 @@
       </c>
       <c r="E42" s="6">
         <f>SUM(E2:E41)</f>
-        <v>1020.9</v>
+        <v>1145.6600000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1140,8 +1162,9 @@
     <hyperlink ref="F8" r:id="rId8" xr:uid="{7BAB4E45-A6E5-B54E-B4E7-980D3A49764F}"/>
     <hyperlink ref="F10" r:id="rId9" xr:uid="{29553635-2A91-4048-BD3A-AA2B63BC1E10}"/>
     <hyperlink ref="F9" r:id="rId10" xr:uid="{AF43F826-6010-5F46-85BE-E2B9217CA3AF}"/>
+    <hyperlink ref="F13" r:id="rId11" xr:uid="{A878F3CB-05D4-4A32-A97B-B6F814AE55A2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId11"/>
+  <pageSetup orientation="portrait" r:id="rId12"/>
 </worksheet>
 </file>